--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/00894-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/00894-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{2705C5CD-79B8-446E-BC7E-DCA5D444EC1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{BFA38C3F-E559-44E9-8B47-A8270F771500}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{B404B447-CF21-4146-9157-C8D993B33C73}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{9C588346-3466-4A2D-9294-CB8DAAAB9401}"/>
   </bookViews>
   <sheets>
     <sheet name="00894-dividend-20260225_0_4" sheetId="2" r:id="rId1"/>
@@ -1555,20 +1555,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8AE72278-A467-4548-BEEE-F95E776420AE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11651E22-E23F-4D5B-9A2E-F0245B9FA13D}">
   <dimension ref="A1:R29"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.77734375" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="11" customWidth="1"/>
+    <col min="3" max="3" width="10.75" customWidth="1"/>
+    <col min="4" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -1596,7 +1596,7 @@
       <c r="Q1" s="32"/>
       <c r="R1" s="24"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="25" t="s">
         <v>1</v>
       </c>
@@ -1626,7 +1626,7 @@
       <c r="Q2" s="34"/>
       <c r="R2" s="35"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="25" t="s">
         <v>2</v>
       </c>
@@ -1672,7 +1672,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="27"/>
       <c r="B4" s="28"/>
       <c r="C4" s="7"/>
@@ -1722,7 +1722,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="39">
         <v>2026</v>
       </c>
@@ -1776,7 +1776,7 @@
         <v>4.68</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="41"/>
       <c r="B6" s="42"/>
       <c r="C6" s="44"/>
@@ -1802,7 +1802,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>27</v>
       </c>
@@ -1858,7 +1858,7 @@
         <v>1.17</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="49">
         <v>2025</v>
       </c>
@@ -1912,7 +1912,7 @@
         <v>7.96</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="19" t="s">
         <v>27</v>
       </c>
@@ -1968,7 +1968,7 @@
         <v>1.5</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="19" t="s">
         <v>27</v>
       </c>
@@ -2024,7 +2024,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="19" t="s">
         <v>27</v>
       </c>
@@ -2080,7 +2080,7 @@
         <v>2.11</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="19" t="s">
         <v>27</v>
       </c>
@@ -2136,7 +2136,7 @@
         <v>2.59</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="51">
         <v>2024</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>7.34</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="11" t="s">
         <v>27</v>
       </c>
@@ -2246,7 +2246,7 @@
         <v>2.85</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="11" t="s">
         <v>27</v>
       </c>
@@ -2302,7 +2302,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="11" t="s">
         <v>27</v>
       </c>
@@ -2358,7 +2358,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
         <v>27</v>
       </c>
@@ -2414,7 +2414,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="49">
         <v>2023</v>
       </c>
@@ -2468,7 +2468,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
         <v>27</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>0.6</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="19" t="s">
         <v>27</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="19" t="s">
         <v>27</v>
       </c>
@@ -2636,7 +2636,7 @@
         <v>0.75</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="19" t="s">
         <v>27</v>
       </c>
@@ -2692,7 +2692,7 @@
         <v>0.77</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="51">
         <v>2022</v>
       </c>
@@ -2746,7 +2746,7 @@
         <v>4.58</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>27</v>
       </c>
@@ -2802,7 +2802,7 @@
         <v>0.83</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>27</v>
       </c>
@@ -2858,7 +2858,7 @@
         <v>1.54</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="11" t="s">
         <v>27</v>
       </c>
@@ -2914,7 +2914,7 @@
         <v>2.21</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="49">
         <v>2021</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="17" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="17" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="19" t="s">
         <v>27</v>
       </c>
@@ -3024,7 +3024,7 @@
         <v>0.38</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="51" t="s">
         <v>56</v>
       </c>
